--- a/data/trans_orig/P16A_2_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26784</t>
+          <t>28627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73481</t>
+          <t>76824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41467</t>
+          <t>43260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78868</t>
+          <t>79990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77630</t>
+          <t>81023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139927</t>
+          <t>139661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326506</t>
+          <t>323163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373203</t>
+          <t>371360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234332</t>
+          <t>233210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271733</t>
+          <t>269940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573260</t>
+          <t>573526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>635557</t>
+          <t>632164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62287</t>
+          <t>60002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104568</t>
+          <t>103746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61285</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123823</t>
+          <t>123184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134268</t>
+          <t>135015</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208336</t>
+          <t>211945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>318979</t>
+          <t>319801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361260</t>
+          <t>363545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388270</t>
+          <t>388909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450808</t>
+          <t>451961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727304</t>
+          <t>723695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801372</t>
+          <t>800625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79692</t>
+          <t>78625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117410</t>
+          <t>116240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126958</t>
+          <t>120147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>188031</t>
+          <t>186383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223798</t>
+          <t>219356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292360</t>
+          <t>291599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>418928</t>
+          <t>420098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>456646</t>
+          <t>457713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>403971</t>
+          <t>405619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>465044</t>
+          <t>471855</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835980</t>
+          <t>836741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>904542</t>
+          <t>908984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>69753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231357</t>
+          <t>233296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>220357</t>
+          <t>216074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286243</t>
+          <t>283234</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258135</t>
+          <t>261587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512721</t>
+          <t>512337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>656429</t>
+          <t>654490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>816759</t>
+          <t>818033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426638</t>
+          <t>429647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>492524</t>
+          <t>496807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1087946</t>
+          <t>1088330</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1342532</t>
+          <t>1339080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145045</t>
+          <t>145308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186127</t>
+          <t>185903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221827</t>
+          <t>219963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>256189</t>
+          <t>255225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>378556</t>
+          <t>375156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>431309</t>
+          <t>432294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>375107</t>
+          <t>375331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>416189</t>
+          <t>415926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>291716</t>
+          <t>292680</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>326078</t>
+          <t>327942</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>677830</t>
+          <t>676845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730583</t>
+          <t>733983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85921</t>
+          <t>87561</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112819</t>
+          <t>115651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>313832</t>
+          <t>311507</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>524515</t>
+          <t>518616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>385787</t>
+          <t>388361</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>726114</t>
+          <t>731033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,86%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255346</t>
+          <t>252514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282244</t>
+          <t>280604</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83853</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>294536</t>
+          <t>296861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250419</t>
+          <t>245500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>590746</t>
+          <t>588172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99438</t>
+          <t>101458</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125997</t>
+          <t>127022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270911</t>
+          <t>270166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298861</t>
+          <t>298170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>378946</t>
+          <t>379507</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>418879</t>
+          <t>417443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156762</t>
+          <t>155737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183321</t>
+          <t>181301</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>126970</t>
+          <t>127661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154920</t>
+          <t>155665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>289711</t>
+          <t>291147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>329644</t>
+          <t>329083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>594040</t>
+          <t>599658</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>847131</t>
+          <t>852926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1367959</t>
+          <t>1371287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1946538</t>
+          <t>1936484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2059043</t>
+          <t>2068179</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2757995</t>
+          <t>2703878</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2612686</t>
+          <t>2606891</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2865777</t>
+          <t>2860159</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1765742</t>
+          <t>1775796</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2344321</t>
+          <t>2340993</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4414102</t>
+          <t>4468219</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5113054</t>
+          <t>5103918</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_2_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76824</t>
+          <t>70972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>71354</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>52562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79990</t>
+          <t>95606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>105925</t>
+          <t>119030</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81023</t>
+          <t>93472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139661</t>
+          <t>155233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>353552</t>
+          <t>360117</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323163</t>
+          <t>336821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>371360</t>
+          <t>378474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>253710</t>
+          <t>291158</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233210</t>
+          <t>266906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269940</t>
+          <t>309950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>607262</t>
+          <t>651275</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573526</t>
+          <t>615072</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>632164</t>
+          <t>676833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,69 +1068,69 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80559</t>
+          <t>88636</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60002</t>
+          <t>66012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>113786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>103976</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>84760</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>122860</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>20,72%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>24,49%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>97484</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>60132</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>123184</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>145</t>
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>178043</t>
+          <t>192612</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135015</t>
+          <t>163278</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211945</t>
+          <t>222962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -1181,67 +1181,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>342988</t>
+          <t>388254</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>319801</t>
+          <t>363104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363545</t>
+          <t>410878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>76,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>397757</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>378873</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>416973</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>79,28%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>75,51%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>414609</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>388909</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>451961</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,96%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>757597</t>
+          <t>786011</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>723695</t>
+          <t>755661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>800625</t>
+          <t>815345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>108173</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78625</t>
+          <t>87748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116240</t>
+          <t>129983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>163912</t>
+          <t>185384</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120147</t>
+          <t>165730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186383</t>
+          <t>205943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>261647</t>
+          <t>293556</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219356</t>
+          <t>266987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291599</t>
+          <t>322299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>438603</t>
+          <t>512664</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420098</t>
+          <t>490854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457713</t>
+          <t>533089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>428090</t>
+          <t>437809</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>405619</t>
+          <t>417250</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>471855</t>
+          <t>457463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>866693</t>
+          <t>950473</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>836741</t>
+          <t>921730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>908984</t>
+          <t>977042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160751</t>
+          <t>172356</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69753</t>
+          <t>148694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>233296</t>
+          <t>196560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>260063</t>
+          <t>274540</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216074</t>
+          <t>254913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>283234</t>
+          <t>295347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>420814</t>
+          <t>446896</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>261587</t>
+          <t>416934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512337</t>
+          <t>481877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>727035</t>
+          <t>528261</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>654490</t>
+          <t>504057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>818033</t>
+          <t>551923</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>452818</t>
+          <t>462346</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>429647</t>
+          <t>441539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496807</t>
+          <t>481973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1179853</t>
+          <t>990608</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1088330</t>
+          <t>955627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1339080</t>
+          <t>1020570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>167352</t>
+          <t>178850</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145308</t>
+          <t>158293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185903</t>
+          <t>200725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>238581</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>219963</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>255225</t>
+          <t>284036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>405932</t>
+          <t>443554</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>375156</t>
+          <t>414432</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432294</t>
+          <t>474159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>393882</t>
+          <t>430496</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>375331</t>
+          <t>408621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>415926</t>
+          <t>451053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>309324</t>
+          <t>344152</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>292680</t>
+          <t>324819</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>327942</t>
+          <t>362019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>703207</t>
+          <t>774648</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>676845</t>
+          <t>744043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>733983</t>
+          <t>803770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>109141</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87561</t>
+          <t>95612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115651</t>
+          <t>124696</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>417128</t>
+          <t>230620</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>311507</t>
+          <t>215956</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>518616</t>
+          <t>245189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>517683</t>
+          <t>339761</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>388361</t>
+          <t>318963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>731033</t>
+          <t>363801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>267609</t>
+          <t>297939</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252514</t>
+          <t>282384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280604</t>
+          <t>311468</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>191240</t>
+          <t>208546</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89752</t>
+          <t>193977</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>296861</t>
+          <t>223210</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>458850</t>
+          <t>506485</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245500</t>
+          <t>482445</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>588172</t>
+          <t>527283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>113511</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101458</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127022</t>
+          <t>137537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>285297</t>
+          <t>309062</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270166</t>
+          <t>292125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298170</t>
+          <t>322458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>398808</t>
+          <t>432266</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>379507</t>
+          <t>410221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>417443</t>
+          <t>452965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>169248</t>
+          <t>186995</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>172661</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>181301</t>
+          <t>201708</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>140534</t>
+          <t>155547</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127661</t>
+          <t>142151</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155665</t>
+          <t>172484</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>309782</t>
+          <t>342541</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>291147</t>
+          <t>321842</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>329083</t>
+          <t>364586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>766900</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>599658</t>
+          <t>775545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>852926</t>
+          <t>887853</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1521954</t>
+          <t>1439640</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1371287</t>
+          <t>1390477</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1936484</t>
+          <t>1492474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2288854</t>
+          <t>2267675</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2068179</t>
+          <t>2189604</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2703878</t>
+          <t>2347341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2692917</t>
+          <t>2704727</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2606891</t>
+          <t>2644909</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2860159</t>
+          <t>2757217</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2190326</t>
+          <t>2297314</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1775796</t>
+          <t>2244480</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2340993</t>
+          <t>2346477</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4883243</t>
+          <t>5002041</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4468219</t>
+          <t>4922375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5103918</t>
+          <t>5080112</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
